--- a/artfynd/A 47-2024 artfynd.xlsx
+++ b/artfynd/A 47-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120030627</v>
+        <v>120030655</v>
       </c>
       <c r="B2" t="n">
-        <v>102217</v>
+        <v>94321</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223246</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>319621</v>
+        <v>319493</v>
       </c>
       <c r="R2" t="n">
-        <v>6418910</v>
+        <v>6419204</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,17 +740,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Kungälv</t>
+          <t>Ytterby</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>täcker stora markområden. Över 100 kvm.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120030628</v>
+        <v>120030627</v>
       </c>
       <c r="B3" t="n">
         <v>102217</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>319605</v>
+        <v>319621</v>
       </c>
       <c r="R3" t="n">
-        <v>6418912</v>
+        <v>6418910</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120030655</v>
+        <v>120030628</v>
       </c>
       <c r="B4" t="n">
-        <v>94321</v>
+        <v>102217</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>223246</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>319493</v>
+        <v>319605</v>
       </c>
       <c r="R4" t="n">
-        <v>6419204</v>
+        <v>6418912</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -944,22 +949,17 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Ytterby</t>
+          <t>Kungälv</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>täcker stora markområden. Över 100 kvm.</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 47-2024 artfynd.xlsx
+++ b/artfynd/A 47-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120030655</v>
+        <v>120030627</v>
       </c>
       <c r="B2" t="n">
-        <v>94321</v>
+        <v>102217</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>223246</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>319493</v>
+        <v>319621</v>
       </c>
       <c r="R2" t="n">
-        <v>6419204</v>
+        <v>6418910</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,22 +740,17 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Ytterby</t>
+          <t>Kungälv</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>täcker stora markområden. Över 100 kvm.</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120030627</v>
+        <v>120030655</v>
       </c>
       <c r="B3" t="n">
-        <v>102217</v>
+        <v>94321</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223246</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>319621</v>
+        <v>319493</v>
       </c>
       <c r="R3" t="n">
-        <v>6418910</v>
+        <v>6419204</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,17 +842,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Kungälv</t>
+          <t>Ytterby</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>täcker stora markområden. Över 100 kvm.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 47-2024 artfynd.xlsx
+++ b/artfynd/A 47-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120030627</v>
       </c>
       <c r="B2" t="n">
-        <v>102217</v>
+        <v>102240</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>120030655</v>
       </c>
       <c r="B3" t="n">
-        <v>94321</v>
+        <v>94344</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>120030628</v>
       </c>
       <c r="B4" t="n">
-        <v>102217</v>
+        <v>102240</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 47-2024 artfynd.xlsx
+++ b/artfynd/A 47-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120030655</v>
+        <v>120030628</v>
       </c>
       <c r="B3" t="n">
-        <v>94344</v>
+        <v>102240</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>223246</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>319493</v>
+        <v>319605</v>
       </c>
       <c r="R3" t="n">
-        <v>6419204</v>
+        <v>6418912</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,22 +842,17 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Ytterby</t>
+          <t>Kungälv</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>täcker stora markområden. Över 100 kvm.</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120030628</v>
+        <v>120030655</v>
       </c>
       <c r="B4" t="n">
-        <v>102240</v>
+        <v>94344</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223246</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>319605</v>
+        <v>319493</v>
       </c>
       <c r="R4" t="n">
-        <v>6418912</v>
+        <v>6419204</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,17 +944,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Kungälv</t>
+          <t>Ytterby</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>täcker stora markområden. Över 100 kvm.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 47-2024 artfynd.xlsx
+++ b/artfynd/A 47-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120030627</v>
+        <v>120030655</v>
       </c>
       <c r="B2" t="n">
-        <v>102240</v>
+        <v>94344</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223246</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>319621</v>
+        <v>319493</v>
       </c>
       <c r="R2" t="n">
-        <v>6418910</v>
+        <v>6419204</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,17 +740,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Kungälv</t>
+          <t>Ytterby</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>täcker stora markområden. Över 100 kvm.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120030628</v>
+        <v>120030627</v>
       </c>
       <c r="B3" t="n">
         <v>102240</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>319605</v>
+        <v>319621</v>
       </c>
       <c r="R3" t="n">
-        <v>6418912</v>
+        <v>6418910</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120030655</v>
+        <v>120030628</v>
       </c>
       <c r="B4" t="n">
-        <v>94344</v>
+        <v>102240</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>223246</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>319493</v>
+        <v>319605</v>
       </c>
       <c r="R4" t="n">
-        <v>6419204</v>
+        <v>6418912</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -944,22 +949,17 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Ytterby</t>
+          <t>Kungälv</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>täcker stora markområden. Över 100 kvm.</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 47-2024 artfynd.xlsx
+++ b/artfynd/A 47-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120030655</v>
+        <v>120030627</v>
       </c>
       <c r="B2" t="n">
-        <v>94344</v>
+        <v>102240</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>223246</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>319493</v>
+        <v>319621</v>
       </c>
       <c r="R2" t="n">
-        <v>6419204</v>
+        <v>6418910</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,22 +740,17 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Ytterby</t>
+          <t>Kungälv</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>täcker stora markområden. Över 100 kvm.</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120030627</v>
+        <v>120030655</v>
       </c>
       <c r="B3" t="n">
-        <v>102240</v>
+        <v>94344</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223246</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>319621</v>
+        <v>319493</v>
       </c>
       <c r="R3" t="n">
-        <v>6418910</v>
+        <v>6419204</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,17 +842,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Kungälv</t>
+          <t>Ytterby</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>täcker stora markområden. Över 100 kvm.</t>
         </is>
       </c>
       <c r="AD3" t="b">
